--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.22023300505533</v>
+        <v>6.373287863321491</v>
       </c>
       <c r="D2" t="n">
-        <v>39.39230662158285</v>
+        <v>6.401249826007214</v>
       </c>
       <c r="E2" t="n">
-        <v>11.44799268418776</v>
+        <v>1.860298811180511</v>
       </c>
       <c r="F2" t="n">
-        <v>10.75342265875977</v>
+        <v>1.747431182048463</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.14943932786112</v>
+        <v>6.361783890777433</v>
       </c>
       <c r="D3" t="n">
-        <v>39.18023628906423</v>
+        <v>6.366788396972937</v>
       </c>
       <c r="E3" t="n">
-        <v>11.44799268418776</v>
+        <v>1.860298811180511</v>
       </c>
       <c r="F3" t="n">
-        <v>10.75342265875977</v>
+        <v>1.747431182048463</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.69562033314812</v>
+        <v>7.42553830413657</v>
       </c>
       <c r="D4" t="n">
-        <v>45.45969350123239</v>
+        <v>7.387200193950263</v>
       </c>
       <c r="E4" t="n">
-        <v>11.44799268418776</v>
+        <v>1.860298811180511</v>
       </c>
       <c r="F4" t="n">
-        <v>10.75342265875977</v>
+        <v>1.747431182048463</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.69255864542247</v>
+        <v>7.750040779881151</v>
       </c>
       <c r="D5" t="n">
-        <v>47.88966304366632</v>
+        <v>7.782070244595778</v>
       </c>
       <c r="E5" t="n">
-        <v>11.44799268418776</v>
+        <v>1.860298811180511</v>
       </c>
       <c r="F5" t="n">
-        <v>10.75342265875977</v>
+        <v>1.747431182048463</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.61842647109057</v>
+        <v>4.325494301552218</v>
       </c>
       <c r="D6" t="n">
-        <v>26.43151028934033</v>
+        <v>4.295120422017805</v>
       </c>
       <c r="E6" t="n">
-        <v>11.44799268418776</v>
+        <v>1.860298811180511</v>
       </c>
       <c r="F6" t="n">
-        <v>10.75342265875977</v>
+        <v>1.747431182048463</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.75931974828135</v>
+        <v>7.11088945909572</v>
       </c>
       <c r="D7" t="n">
-        <v>43.81914600000174</v>
+        <v>7.120611225000284</v>
       </c>
       <c r="E7" t="n">
-        <v>11.44799268418776</v>
+        <v>1.860298811180511</v>
       </c>
       <c r="F7" t="n">
-        <v>10.75342265875977</v>
+        <v>1.747431182048463</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.20183883982964</v>
+        <v>2.145298811472317</v>
       </c>
       <c r="D8" t="n">
-        <v>15.76814822539703</v>
+        <v>2.562324086627017</v>
       </c>
       <c r="E8" t="n">
-        <v>11.44799268418776</v>
+        <v>1.860298811180511</v>
       </c>
       <c r="F8" t="n">
-        <v>10.75342265875977</v>
+        <v>1.747431182048463</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
